--- a/artfynd/A 55009-2022 artfynd.xlsx
+++ b/artfynd/A 55009-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 55009-2022 artfynd.xlsx
+++ b/artfynd/A 55009-2022 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>56071189</v>
+        <v>56071190</v>
       </c>
       <c r="B2" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>675644.7941401203</v>
+        <v>675645</v>
       </c>
       <c r="R2" t="n">
-        <v>7094606.80470792</v>
+        <v>7094607</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,19 +747,9 @@
           <t>2015-09-08</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2015-09-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>56071190</v>
+        <v>56826342</v>
       </c>
       <c r="B3" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,38 +787,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>6456</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sundsjöarna, Ång</t>
+          <t>Sundsjöarna syd, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>675644.7941401203</v>
+        <v>675705</v>
       </c>
       <c r="R3" t="n">
-        <v>7094606.80470792</v>
+        <v>7094547</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,22 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2015-09-08</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-05-18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2015-09-08</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-10-30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,16 +857,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Julia Pettersson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Julia Pettersson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -910,12 +886,7 @@
         <v>56826344</v>
       </c>
       <c r="B4" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -947,10 +918,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>675604.9024690163</v>
+        <v>675605</v>
       </c>
       <c r="R4" t="n">
-        <v>7094617.781752333</v>
+        <v>7094618</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,19 +951,9 @@
           <t>2015-05-18</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2015-10-30</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1032,12 +993,7 @@
         <v>56826345</v>
       </c>
       <c r="B5" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1069,10 +1025,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>675381.9272556243</v>
+        <v>675382</v>
       </c>
       <c r="R5" t="n">
-        <v>7094737.896601757</v>
+        <v>7094738</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1102,19 +1058,9 @@
           <t>2015-05-18</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2015-10-30</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1151,50 +1097,49 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>56826342</v>
+        <v>56071189</v>
       </c>
       <c r="B6" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6456</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sundsjöarna syd, Ång</t>
+          <t>Sundsjöarna, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>675705.0758763043</v>
+        <v>675645</v>
       </c>
       <c r="R6" t="n">
-        <v>7094547.174752596</v>
+        <v>7094607</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1221,22 +1166,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2015-05-18</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-09-08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2015-10-30</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-09-08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1247,26 +1182,16 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Julia Pettersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Julia Pettersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 55009-2022 artfynd.xlsx
+++ b/artfynd/A 55009-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56071190</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56826342</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56826344</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1094,6 +1114,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56826345</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1195,8 +1220,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56071189</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>